--- a/data/trans_bre/P16A08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A08-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,45</t>
+          <t>-3,47; 1,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 7,12</t>
+          <t>-0,51; 7,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,66</t>
+          <t>-2,6; 4,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,84; -1,38</t>
+          <t>-9,97; -1,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-88,83; 172,6</t>
+          <t>-90,91; 192,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 315,77</t>
+          <t>-15,75; 336,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,36; 210,85</t>
+          <t>-51,32; 197,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-90,04; -31,25</t>
+          <t>-89,6; -23,33</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,71</t>
+          <t>1,74; 6,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,96</t>
+          <t>-2,59; 4,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,9</t>
+          <t>1,61; 6,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 3,66</t>
+          <t>-2,6; 3,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,01; 506,99</t>
+          <t>41,64; 531,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 85,8</t>
+          <t>-32,2; 89,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,21; 387,9</t>
+          <t>31,41; 377,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 120,62</t>
+          <t>-36,86; 127,74</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,57</t>
+          <t>0,01; 4,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,34</t>
+          <t>1,89; 8,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,59</t>
+          <t>-2,51; 2,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,58</t>
+          <t>-3,91; 1,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-74,55; —</t>
+          <t>-45,4; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,5; 787,59</t>
+          <t>37,97; 742,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,84; 165,66</t>
+          <t>-59,77; 190,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,55; 129,37</t>
+          <t>-73,36; 113,62</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,59</t>
+          <t>-1,71; 3,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,63</t>
+          <t>-0,16; 4,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 5,94</t>
+          <t>-1,18; 5,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 48,7</t>
+          <t>-0,04; 44,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 314,83</t>
+          <t>-49,52; 278,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 537,67</t>
+          <t>-19,32; 459,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 221,57</t>
+          <t>-23,29; 210,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,53; —</t>
+          <t>-23,87; 13897,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 9,94</t>
+          <t>1,12; 10,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,26</t>
+          <t>0,81; 10,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 5,56</t>
+          <t>-0,52; 5,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,17</t>
+          <t>-3,31; 3,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 627,61</t>
+          <t>9,26; 681,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,12; 456,22</t>
+          <t>-0,05; 446,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 609,09</t>
+          <t>-31,97; 685,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,76; 173,27</t>
+          <t>-58,39; 189,08</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,68</t>
+          <t>-0,89; 4,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 4,75</t>
+          <t>-1,95; 5,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 5,36</t>
+          <t>-2,45; 4,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,03</t>
+          <t>-1,58; 3,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 766,19</t>
+          <t>-50,13; 609,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 206,3</t>
+          <t>-43,42; 254,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 266,27</t>
+          <t>-49,32; 224,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,6; 310,81</t>
+          <t>-46,0; 294,7</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,17</t>
+          <t>-0,48; 3,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,46</t>
+          <t>0,78; 4,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,81</t>
+          <t>1,19; 5,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,41</t>
+          <t>-0,99; 5,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 383,63</t>
+          <t>-29,69; 347,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,97; 562,41</t>
+          <t>21,47; 501,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,64; 446,32</t>
+          <t>29,46; 396,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 266,33</t>
+          <t>-20,97; 255,5</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,95</t>
+          <t>-1,92; 2,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,36</t>
+          <t>-1,78; 2,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,96</t>
+          <t>-0,18; 3,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,96</t>
+          <t>1,66; 6,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 73,15</t>
+          <t>-39,52; 71,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 89,26</t>
+          <t>-35,69; 79,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 172,63</t>
+          <t>-6,46; 155,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,37; 450,4</t>
+          <t>42,68; 492,55</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,4</t>
+          <t>0,64; 2,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,07</t>
+          <t>1,09; 3,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,35</t>
+          <t>1,4; 3,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 9,9</t>
+          <t>0,8; 10,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,03; 121,72</t>
+          <t>22,13; 120,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,38; 101,25</t>
+          <t>28,35; 108,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,06; 126,06</t>
+          <t>39,55; 124,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,15; 336,51</t>
+          <t>22,8; 330,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A08-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,48</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-70,39%</t>
+          <t>-43,81%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,62</t>
+          <t>-3,15; 1,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 7,14</t>
+          <t>-0,52; 7,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,22</t>
+          <t>-2,48; 4,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,97; -1,11</t>
+          <t>-5,83; 1,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-90,91; 192,65</t>
+          <t>-85,77; 216,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 336,52</t>
+          <t>-18,56; 351,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,32; 197,51</t>
+          <t>-50,7; 178,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-89,6; -23,33</t>
+          <t>-78,15; 48,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,68</t>
+          <t>1,37; 6,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 4,31</t>
+          <t>-2,86; 4,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,85</t>
+          <t>1,51; 6,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,32</t>
+          <t>-2,53; 3,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,64; 531,18</t>
+          <t>27,22; 522,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 89,0</t>
+          <t>-33,51; 87,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,41; 377,31</t>
+          <t>34,94; 405,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 127,74</t>
+          <t>-38,54; 108,68</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-22,97%</t>
+          <t>-26,08%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,27</t>
+          <t>0,03; 4,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,81</t>
+          <t>1,97; 8,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,63</t>
+          <t>-2,6; 2,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,44</t>
+          <t>-3,47; 1,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,4; —</t>
+          <t>-46,96; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,97; 742,02</t>
+          <t>32,74; 809,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,77; 190,12</t>
+          <t>-57,92; 174,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,36; 113,62</t>
+          <t>-71,64; 101,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,06</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>827,96%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,58</t>
+          <t>-1,61; 3,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,7</t>
+          <t>-0,22; 4,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,74</t>
+          <t>-1,1; 5,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 44,22</t>
+          <t>-1,65; 3,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 278,0</t>
+          <t>-47,89; 271,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 459,64</t>
+          <t>-20,33; 477,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 210,39</t>
+          <t>-24,47; 219,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 13897,29</t>
+          <t>-56,91; 507,63</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,86</t>
+          <t>0,96; 10,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 10,35</t>
+          <t>0,8; 10,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,8</t>
+          <t>-0,37; 6,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 3,22</t>
+          <t>-3,03; 3,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,26; 681,0</t>
+          <t>0,43; 570,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 446,62</t>
+          <t>4,5; 370,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,97; 685,13</t>
+          <t>-29,26; 721,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,39; 189,08</t>
+          <t>-54,46; 203,49</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,36</t>
+          <t>-0,91; 4,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 5,04</t>
+          <t>-1,92; 5,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,84</t>
+          <t>-2,14; 5,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,98</t>
+          <t>-1,68; 4,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 609,58</t>
+          <t>-55,11; 839,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 254,49</t>
+          <t>-37,53; 284,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,32; 224,64</t>
+          <t>-46,73; 220,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 294,7</t>
+          <t>-47,83; 362,46</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>4,27</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>107,19%</t>
+          <t>139,28%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,15</t>
+          <t>-0,35; 2,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,58</t>
+          <t>0,83; 4,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,75</t>
+          <t>1,25; 5,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 5,52</t>
+          <t>2,2; 6,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 347,94</t>
+          <t>-24,35; 319,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,47; 501,29</t>
+          <t>21,34; 515,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,46; 396,16</t>
+          <t>27,12; 424,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 255,5</t>
+          <t>48,86; 304,44</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>142,51%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,02</t>
+          <t>-2,2; 2,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,23</t>
+          <t>-1,67; 2,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,78</t>
+          <t>-0,03; 3,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,16</t>
+          <t>1,09; 5,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,52; 71,83</t>
+          <t>-44,49; 75,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,69; 79,67</t>
+          <t>-34,5; 87,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 155,37</t>
+          <t>-1,91; 166,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,68; 492,55</t>
+          <t>23,03; 233,21</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,37</t>
+          <t>0,74; 2,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,15</t>
+          <t>1,09; 3,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,27</t>
+          <t>1,37; 3,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 10,65</t>
+          <t>0,59; 2,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,13; 120,77</t>
+          <t>25,93; 123,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,35; 108,2</t>
+          <t>27,76; 103,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,55; 124,15</t>
+          <t>38,82; 122,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22,8; 330,72</t>
+          <t>14,09; 85,7</t>
         </is>
       </c>
     </row>
